--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/82.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/82.xlsx
@@ -426,13 +426,13 @@
         <v>-1.303787695361722</v>
       </c>
       <c r="E2">
-        <v>-7.979168749748764</v>
+        <v>-0.6705015237052981</v>
       </c>
       <c r="F2">
-        <v>-5.36942049484311</v>
+        <v>-2.776834302461746</v>
       </c>
       <c r="G2">
-        <v>-6.071131583324452</v>
+        <v>-5.105937293062873</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.239764682973836</v>
       </c>
       <c r="E3">
-        <v>-7.872966977320879</v>
+        <v>-1.494058863688245</v>
       </c>
       <c r="F3">
-        <v>-5.027488655050336</v>
+        <v>-2.576183836686039</v>
       </c>
       <c r="G3">
-        <v>-6.66311645219323</v>
+        <v>-3.813280372390271</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.462150083040088</v>
       </c>
       <c r="E4">
-        <v>-8.923464263724219</v>
+        <v>-2.245708564903393</v>
       </c>
       <c r="F4">
-        <v>-5.277730992129441</v>
+        <v>-2.722683925340742</v>
       </c>
       <c r="G4">
-        <v>-6.151249170141414</v>
+        <v>-4.22591695204136</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.917003361903382</v>
       </c>
       <c r="E5">
-        <v>-8.750168620398689</v>
+        <v>-2.542572678476224</v>
       </c>
       <c r="F5">
-        <v>-5.251156965847633</v>
+        <v>-2.769277935013409</v>
       </c>
       <c r="G5">
-        <v>-6.006038710028188</v>
+        <v>-3.38972060616779</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.498423637742654</v>
       </c>
       <c r="E6">
-        <v>-10.07604241120846</v>
+        <v>-3.570549863639418</v>
       </c>
       <c r="F6">
-        <v>-5.09487468653327</v>
+        <v>-2.593088330274968</v>
       </c>
       <c r="G6">
-        <v>-5.99485958817516</v>
+        <v>-3.70036041364354</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.095555794677737</v>
       </c>
       <c r="E7">
-        <v>-10.23804404035886</v>
+        <v>-3.98116471581092</v>
       </c>
       <c r="F7">
-        <v>-5.217429987042651</v>
+        <v>-2.340456981606189</v>
       </c>
       <c r="G7">
-        <v>-5.77716366259224</v>
+        <v>-3.627943853826595</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.60837456094103</v>
       </c>
       <c r="E8">
-        <v>-11.09190592840114</v>
+        <v>-4.943320531272626</v>
       </c>
       <c r="F8">
-        <v>-5.356821026646529</v>
+        <v>-2.416959196356931</v>
       </c>
       <c r="G8">
-        <v>-5.40419048915172</v>
+        <v>-3.59027871154573</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.958809837157435</v>
       </c>
       <c r="E9">
-        <v>-11.04303010843635</v>
+        <v>-4.957924859947362</v>
       </c>
       <c r="F9">
-        <v>-5.430169646694814</v>
+        <v>-2.455711051827295</v>
       </c>
       <c r="G9">
-        <v>-5.244670621817755</v>
+        <v>-3.839254522254835</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.100124828341476</v>
       </c>
       <c r="E10">
-        <v>-11.86100383996784</v>
+        <v>-5.86664015364455</v>
       </c>
       <c r="F10">
-        <v>-5.583129344356549</v>
+        <v>-2.444297805751524</v>
       </c>
       <c r="G10">
-        <v>-5.117395318748454</v>
+        <v>-1.69600325550582</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.018064465959036</v>
       </c>
       <c r="E11">
-        <v>-11.48231472955042</v>
+        <v>-6.353740931805604</v>
       </c>
       <c r="F11">
-        <v>-5.275954144050436</v>
+        <v>-2.357120420280904</v>
       </c>
       <c r="G11">
-        <v>-4.613271719576927</v>
+        <v>-1.792710698527334</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.728043680182001</v>
       </c>
       <c r="E12">
-        <v>-12.87725680592518</v>
+        <v>-6.947514443691341</v>
       </c>
       <c r="F12">
-        <v>-5.491531790424591</v>
+        <v>-2.305054215545344</v>
       </c>
       <c r="G12">
-        <v>-4.011725371083927</v>
+        <v>-2.152585235502552</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.268963512722134</v>
       </c>
       <c r="E13">
-        <v>-12.92054901743851</v>
+        <v>-7.624879057284666</v>
       </c>
       <c r="F13">
-        <v>-5.25317404047345</v>
+        <v>-1.839713856818305</v>
       </c>
       <c r="G13">
-        <v>-3.319951992149317</v>
+        <v>-1.249593062343366</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.697710342682039</v>
       </c>
       <c r="E14">
-        <v>-14.02875717659559</v>
+        <v>-9.2047141989186</v>
       </c>
       <c r="F14">
-        <v>-5.280419044351525</v>
+        <v>-1.537533711951073</v>
       </c>
       <c r="G14">
-        <v>-2.983958185683738</v>
+        <v>-0.7912326602614148</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.081687674508687</v>
       </c>
       <c r="E15">
-        <v>-14.94407045692196</v>
+        <v>-9.503638768164921</v>
       </c>
       <c r="F15">
-        <v>-5.007032122038201</v>
+        <v>-1.690489267775793</v>
       </c>
       <c r="G15">
-        <v>-1.623944348838854</v>
+        <v>-0.3621538793759482</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.489496565911925</v>
       </c>
       <c r="E16">
-        <v>-15.23713518080235</v>
+        <v>-9.99055387889166</v>
       </c>
       <c r="F16">
-        <v>-5.18802625771288</v>
+        <v>-1.636222090850995</v>
       </c>
       <c r="G16">
-        <v>-1.527880025242991</v>
+        <v>0.3643184175497902</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.9791932066446443</v>
       </c>
       <c r="E17">
-        <v>-16.85985044281492</v>
+        <v>-10.87200775906267</v>
       </c>
       <c r="F17">
-        <v>-4.982011284636643</v>
+        <v>-1.358508605592849</v>
       </c>
       <c r="G17">
-        <v>-1.294969075288927</v>
+        <v>0.951440516067471</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.5971166949124377</v>
       </c>
       <c r="E18">
-        <v>-17.6050244261991</v>
+        <v>-12.10175563211163</v>
       </c>
       <c r="F18">
-        <v>-4.490373574340331</v>
+        <v>-1.020551272598707</v>
       </c>
       <c r="G18">
-        <v>-1.133559224336723</v>
+        <v>0.1357452424973119</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.3726853185125866</v>
       </c>
       <c r="E19">
-        <v>-18.61996413469421</v>
+        <v>-13.81073379549631</v>
       </c>
       <c r="F19">
-        <v>-4.176325409693191</v>
+        <v>-0.7224765165797498</v>
       </c>
       <c r="G19">
-        <v>-0.726586033097235</v>
+        <v>0.4510903216893057</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.3144338381177696</v>
       </c>
       <c r="E20">
-        <v>-18.61086190193879</v>
+        <v>-14.04921682216225</v>
       </c>
       <c r="F20">
-        <v>-3.939008917567369</v>
+        <v>-0.4517925571017609</v>
       </c>
       <c r="G20">
-        <v>-0.5682736552971464</v>
+        <v>1.726842388887649</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.4081521457653808</v>
       </c>
       <c r="E21">
-        <v>-18.45486502932256</v>
+        <v>-14.20408610475057</v>
       </c>
       <c r="F21">
-        <v>-3.833719278834537</v>
+        <v>-0.3566852104841413</v>
       </c>
       <c r="G21">
-        <v>-0.5038928070792815</v>
+        <v>1.255888658460549</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.6253703709372869</v>
       </c>
       <c r="E22">
-        <v>-19.36203611338314</v>
+        <v>-15.56869193374795</v>
       </c>
       <c r="F22">
-        <v>-3.474245102552678</v>
+        <v>-0.0610839595299433</v>
       </c>
       <c r="G22">
-        <v>-1.785751227599751</v>
+        <v>1.923262873879129</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.9249546255962973</v>
       </c>
       <c r="E23">
-        <v>-19.3048052588742</v>
+        <v>-17.05309854261824</v>
       </c>
       <c r="F23">
-        <v>-3.454853021653141</v>
+        <v>0.7249199059229928</v>
       </c>
       <c r="G23">
-        <v>-1.500386669796404</v>
+        <v>1.276537385734134</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.26014978003235</v>
       </c>
       <c r="E24">
-        <v>-20.45135600745423</v>
+        <v>-16.83402455554917</v>
       </c>
       <c r="F24">
-        <v>-3.414866070385204</v>
+        <v>-0.01808589275282936</v>
       </c>
       <c r="G24">
-        <v>-1.62461699925854</v>
+        <v>1.174264990947802</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.583823421548737</v>
       </c>
       <c r="E25">
-        <v>-20.67873974432738</v>
+        <v>-16.08801733294758</v>
       </c>
       <c r="F25">
-        <v>-3.034659514746078</v>
+        <v>0.9096160155207818</v>
       </c>
       <c r="G25">
-        <v>-2.182352477489834</v>
+        <v>1.376936203010024</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.855065801712679</v>
       </c>
       <c r="E26">
-        <v>-20.30244619666001</v>
+        <v>-16.42775703842504</v>
       </c>
       <c r="F26">
-        <v>-3.023392061333199</v>
+        <v>0.6872026813387258</v>
       </c>
       <c r="G26">
-        <v>-2.081064449171335</v>
+        <v>2.236458752949686</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.038660734426471</v>
       </c>
       <c r="E27">
-        <v>-20.42534445275417</v>
+        <v>-17.59680977434919</v>
       </c>
       <c r="F27">
-        <v>-2.732379137423108</v>
+        <v>0.5715120614963439</v>
       </c>
       <c r="G27">
-        <v>-2.510494320763662</v>
+        <v>1.110927571185841</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.107780674570889</v>
       </c>
       <c r="E28">
-        <v>-20.33146012962715</v>
+        <v>-17.50402587040602</v>
       </c>
       <c r="F28">
-        <v>-2.84128211476695</v>
+        <v>0.7057763352442962</v>
       </c>
       <c r="G28">
-        <v>-2.543024351303997</v>
+        <v>-0.2011869933342688</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.046250427881951</v>
       </c>
       <c r="E29">
-        <v>-20.83899338251081</v>
+        <v>-15.81753158046943</v>
       </c>
       <c r="F29">
-        <v>-2.879273528961544</v>
+        <v>0.3152872550342205</v>
       </c>
       <c r="G29">
-        <v>-3.069647286708637</v>
+        <v>-0.3963835826840754</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.848971964564825</v>
       </c>
       <c r="E30">
-        <v>-20.20804562749611</v>
+        <v>-16.28224811161057</v>
       </c>
       <c r="F30">
-        <v>-2.807649569845888</v>
+        <v>0.7177097960490258</v>
       </c>
       <c r="G30">
-        <v>-3.158968699999841</v>
+        <v>-0.1062612536195331</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.521791879898125</v>
       </c>
       <c r="E31">
-        <v>-20.30075707585515</v>
+        <v>-16.52429504732055</v>
       </c>
       <c r="F31">
-        <v>-2.620680420094817</v>
+        <v>0.4330761295078934</v>
       </c>
       <c r="G31">
-        <v>-2.715462387917496</v>
+        <v>0.5622023273567821</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.08067569803118</v>
       </c>
       <c r="E32">
-        <v>-20.52038353675315</v>
+        <v>-15.30739898350537</v>
       </c>
       <c r="F32">
-        <v>-2.91124105540298</v>
+        <v>0.5164049200251069</v>
       </c>
       <c r="G32">
-        <v>-3.301964335560441</v>
+        <v>0.3363591286417618</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.5489258090530247</v>
       </c>
       <c r="E33">
-        <v>-19.77752360358689</v>
+        <v>-15.79310046319805</v>
       </c>
       <c r="F33">
-        <v>-2.920666219712033</v>
+        <v>0.500435653233938</v>
       </c>
       <c r="G33">
-        <v>-2.974944670059943</v>
+        <v>0.4282005200906194</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.04569056769627737</v>
       </c>
       <c r="E34">
-        <v>-19.38624533542814</v>
+        <v>-15.10259874650848</v>
       </c>
       <c r="F34">
-        <v>-2.795897521502371</v>
+        <v>0.2035239250485112</v>
       </c>
       <c r="G34">
-        <v>-2.467044384873495</v>
+        <v>0.2026132566572358</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.6696035131287159</v>
       </c>
       <c r="E35">
-        <v>-19.14917519265259</v>
+        <v>-15.00560336173818</v>
       </c>
       <c r="F35">
-        <v>-2.645491680543468</v>
+        <v>0.4900164480415258</v>
       </c>
       <c r="G35">
-        <v>-3.047541697062657</v>
+        <v>0.2549848339675329</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.283668667169771</v>
       </c>
       <c r="E36">
-        <v>-18.6141133462763</v>
+        <v>-13.64077563751443</v>
       </c>
       <c r="F36">
-        <v>-2.580235381653131</v>
+        <v>0.4314856640945183</v>
       </c>
       <c r="G36">
-        <v>-2.891755859863341</v>
+        <v>0.8286473616483714</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.849120705766459</v>
       </c>
       <c r="E37">
-        <v>-18.64461261871796</v>
+        <v>-15.14727214259414</v>
       </c>
       <c r="F37">
-        <v>-2.904806297418033</v>
+        <v>0.528166908777457</v>
       </c>
       <c r="G37">
-        <v>-3.094555039566381</v>
+        <v>0.1766456692357903</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.332226374695526</v>
       </c>
       <c r="E38">
-        <v>-18.7512581815986</v>
+        <v>-13.93239577818638</v>
       </c>
       <c r="F38">
-        <v>-2.738846201736763</v>
+        <v>0.3398359230161838</v>
       </c>
       <c r="G38">
-        <v>-3.467022904886748</v>
+        <v>0.5390861214704942</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.707340814623479</v>
       </c>
       <c r="E39">
-        <v>-17.49723315939452</v>
+        <v>-13.0395708997821</v>
       </c>
       <c r="F39">
-        <v>-2.714190674359839</v>
+        <v>0.5324893298852649</v>
       </c>
       <c r="G39">
-        <v>-2.811625148160142</v>
+        <v>0.9151141121828585</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.958956147262556</v>
       </c>
       <c r="E40">
-        <v>-17.34465528465408</v>
+        <v>-12.59944398250262</v>
       </c>
       <c r="F40">
-        <v>-2.661810518378618</v>
+        <v>0.9544008707857342</v>
       </c>
       <c r="G40">
-        <v>-2.682807670957902</v>
+        <v>1.299617498183269</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>3.083845324646079</v>
       </c>
       <c r="E41">
-        <v>-16.57127343667613</v>
+        <v>-12.44878618074143</v>
       </c>
       <c r="F41">
-        <v>-2.518798684857103</v>
+        <v>0.6791857416144321</v>
       </c>
       <c r="G41">
-        <v>-2.6621359751334</v>
+        <v>1.233290885580653</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>3.08949860871873</v>
       </c>
       <c r="E42">
-        <v>-16.85156333538088</v>
+        <v>-12.13890723287055</v>
       </c>
       <c r="F42">
-        <v>-2.342510504397729</v>
+        <v>0.3097562458857282</v>
       </c>
       <c r="G42">
-        <v>-2.085093789246333</v>
+        <v>1.19153406001516</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.99132338842083</v>
       </c>
       <c r="E43">
-        <v>-16.20943477804124</v>
+        <v>-10.63122879607484</v>
       </c>
       <c r="F43">
-        <v>-2.573526434057858</v>
+        <v>0.3884494924168756</v>
       </c>
       <c r="G43">
-        <v>-1.982801707130644</v>
+        <v>0.9381351626439227</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.809275196904857</v>
       </c>
       <c r="E44">
-        <v>-15.83433221903789</v>
+        <v>-10.97220024648238</v>
       </c>
       <c r="F44">
-        <v>-2.605683656634535</v>
+        <v>0.1363449854162769</v>
       </c>
       <c r="G44">
-        <v>-1.678133722893084</v>
+        <v>1.390353117966593</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>2.564477837523683</v>
       </c>
       <c r="E45">
-        <v>-15.43052819177392</v>
+        <v>-11.48520842444132</v>
       </c>
       <c r="F45">
-        <v>-2.654681588510126</v>
+        <v>0.4683480135190963</v>
       </c>
       <c r="G45">
-        <v>-1.317324037773424</v>
+        <v>2.063846811593538</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>2.278032008120483</v>
       </c>
       <c r="E46">
-        <v>-15.43876548599388</v>
+        <v>-10.90491165120241</v>
       </c>
       <c r="F46">
-        <v>-3.088286363668513</v>
+        <v>0.5803457714797979</v>
       </c>
       <c r="G46">
-        <v>-1.265707141421799</v>
+        <v>1.908425189987319</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.970512718456201</v>
       </c>
       <c r="E47">
-        <v>-14.73673427448077</v>
+        <v>-9.308733246874789</v>
       </c>
       <c r="F47">
-        <v>-2.789519920868218</v>
+        <v>-0.03072015238032742</v>
       </c>
       <c r="G47">
-        <v>-1.877507307288063</v>
+        <v>2.259571677614415</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.660399641972346</v>
       </c>
       <c r="E48">
-        <v>-14.24397743228414</v>
+        <v>-8.975967391369148</v>
       </c>
       <c r="F48">
-        <v>-2.782320579770487</v>
+        <v>0.3389462564255771</v>
       </c>
       <c r="G48">
-        <v>-1.16477348503172</v>
+        <v>2.224984321156308</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.362475124084914</v>
       </c>
       <c r="E49">
-        <v>-13.41879889860644</v>
+        <v>-9.768020137680733</v>
       </c>
       <c r="F49">
-        <v>-2.813736413521658</v>
+        <v>0.03740561119330672</v>
       </c>
       <c r="G49">
-        <v>-1.515463882862052</v>
+        <v>2.577125018915915</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.08797807922386</v>
       </c>
       <c r="E50">
-        <v>-13.16395449535079</v>
+        <v>-8.780002207161221</v>
       </c>
       <c r="F50">
-        <v>-2.522026832625813</v>
+        <v>0.4171698186393373</v>
       </c>
       <c r="G50">
-        <v>-1.178754770096514</v>
+        <v>2.140072869640997</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.8445594032782422</v>
       </c>
       <c r="E51">
-        <v>-13.46498480501067</v>
+        <v>-7.441711340622415</v>
       </c>
       <c r="F51">
-        <v>-2.646184195692208</v>
+        <v>0.2569867572251913</v>
       </c>
       <c r="G51">
-        <v>-1.082099826619951</v>
+        <v>1.638652997034453</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.6355521849260748</v>
       </c>
       <c r="E52">
-        <v>-12.94829950615751</v>
+        <v>-8.592786034736113</v>
       </c>
       <c r="F52">
-        <v>-2.42805766281964</v>
+        <v>0.1449732602838365</v>
       </c>
       <c r="G52">
-        <v>-1.538353684460739</v>
+        <v>2.260805416920766</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.4603289475786912</v>
       </c>
       <c r="E53">
-        <v>-12.18238964029221</v>
+        <v>-7.434474839158158</v>
       </c>
       <c r="F53">
-        <v>-2.778315423377951</v>
+        <v>0.5027194621634562</v>
       </c>
       <c r="G53">
-        <v>-1.486707257115079</v>
+        <v>2.16871793385495</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.3163673544760247</v>
       </c>
       <c r="E54">
-        <v>-12.21393951870365</v>
+        <v>-6.050881118646618</v>
       </c>
       <c r="F54">
-        <v>-2.757772740155926</v>
+        <v>-0.1522689864953073</v>
       </c>
       <c r="G54">
-        <v>-1.303700405858609</v>
+        <v>1.688265067013258</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.1997511999521095</v>
       </c>
       <c r="E55">
-        <v>-11.60015015170401</v>
+        <v>-6.835511696059631</v>
       </c>
       <c r="F55">
-        <v>-2.369427474784296</v>
+        <v>0.03726313200002521</v>
       </c>
       <c r="G55">
-        <v>-1.6371447031725</v>
+        <v>1.882880880147042</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.1059062331941209</v>
       </c>
       <c r="E56">
-        <v>-10.4722159597695</v>
+        <v>-5.69478456505346</v>
       </c>
       <c r="F56">
-        <v>-2.602514322951424</v>
+        <v>0.2670804140283032</v>
       </c>
       <c r="G56">
-        <v>-1.784822641898429</v>
+        <v>1.027325327072749</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.0299600270954437</v>
       </c>
       <c r="E57">
-        <v>-10.84397197648119</v>
+        <v>-6.071857010250148</v>
       </c>
       <c r="F57">
-        <v>-2.330715380949267</v>
+        <v>0.2652008483913512</v>
       </c>
       <c r="G57">
-        <v>-2.14125189623623</v>
+        <v>0.7323205403277528</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.03248205268647412</v>
       </c>
       <c r="E58">
-        <v>-10.40477339637327</v>
+        <v>-4.869103370760916</v>
       </c>
       <c r="F58">
-        <v>-2.458346088535601</v>
+        <v>0.3605235705336987</v>
       </c>
       <c r="G58">
-        <v>-2.207578508838845</v>
+        <v>0.6818980086237659</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.08515577103705819</v>
       </c>
       <c r="E59">
-        <v>-9.862782984765241</v>
+        <v>-5.52378485804982</v>
       </c>
       <c r="F59">
-        <v>-2.322464013249981</v>
+        <v>0.5754360378834052</v>
       </c>
       <c r="G59">
-        <v>-2.534480050363203</v>
+        <v>0.6046055535694862</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.1311410913294565</v>
       </c>
       <c r="E60">
-        <v>-10.00768509606268</v>
+        <v>-4.847312353836006</v>
       </c>
       <c r="F60">
-        <v>-2.254149381908508</v>
+        <v>0.2748761796560494</v>
       </c>
       <c r="G60">
-        <v>-2.708401199121571</v>
+        <v>1.024388633777046</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.172033717348206</v>
       </c>
       <c r="E61">
-        <v>-9.87670351386482</v>
+        <v>-4.190122091946853</v>
       </c>
       <c r="F61">
-        <v>-2.100005947228174</v>
+        <v>0.05461991419088325</v>
       </c>
       <c r="G61">
-        <v>-3.152107665719042</v>
+        <v>0.2630435141175291</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.2078557930586817</v>
       </c>
       <c r="E62">
-        <v>-9.91157729219789</v>
+        <v>-4.684337102773958</v>
       </c>
       <c r="F62">
-        <v>-2.662894022941479</v>
+        <v>0.2442058765673977</v>
       </c>
       <c r="G62">
-        <v>-2.967066457095716</v>
+        <v>-0.2397544715439819</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.2388248932530228</v>
       </c>
       <c r="E63">
-        <v>-9.467352105941458</v>
+        <v>-3.716969013729424</v>
       </c>
       <c r="F63">
-        <v>-2.163060445561869</v>
+        <v>0.1970129572625071</v>
       </c>
       <c r="G63">
-        <v>-3.620859696479754</v>
+        <v>-0.4441942620267444</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.2663636619990185</v>
       </c>
       <c r="E64">
-        <v>-9.623702199530285</v>
+        <v>-3.533466189990605</v>
       </c>
       <c r="F64">
-        <v>-2.331908230009298</v>
+        <v>0.2712570424732184</v>
       </c>
       <c r="G64">
-        <v>-3.309402864835703</v>
+        <v>-0.7295981944888053</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.293932608204599</v>
       </c>
       <c r="E65">
-        <v>-9.107111998631282</v>
+        <v>-4.476751854262349</v>
       </c>
       <c r="F65">
-        <v>-2.384549321722401</v>
+        <v>0.3829797824561905</v>
       </c>
       <c r="G65">
-        <v>-3.432537266296984</v>
+        <v>-1.198071321416965</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.3267310987913737</v>
       </c>
       <c r="E66">
-        <v>-9.038659585531336</v>
+        <v>-3.550724204433837</v>
       </c>
       <c r="F66">
-        <v>-2.337606569373156</v>
+        <v>0.1936398451983075</v>
       </c>
       <c r="G66">
-        <v>-3.772786817125164</v>
+        <v>-1.073847554397948</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.371896722537377</v>
       </c>
       <c r="E67">
-        <v>-8.643627212420228</v>
+        <v>-3.557073124992591</v>
       </c>
       <c r="F67">
-        <v>-2.197817913415934</v>
+        <v>0.5367347128246123</v>
       </c>
       <c r="G67">
-        <v>-3.816600968608429</v>
+        <v>-0.8974753331346752</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.436501288992854</v>
       </c>
       <c r="E68">
-        <v>-8.476467651375092</v>
+        <v>-3.256246596663049</v>
       </c>
       <c r="F68">
-        <v>-2.474423871456536</v>
+        <v>0.1238151000815316</v>
       </c>
       <c r="G68">
-        <v>-4.328044973079076</v>
+        <v>-1.52894970347137</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.5274135494204316</v>
       </c>
       <c r="E69">
-        <v>-8.80749004438778</v>
+        <v>-2.720985497430421</v>
       </c>
       <c r="F69">
-        <v>-2.234516246094757</v>
+        <v>-0.1362284801074976</v>
       </c>
       <c r="G69">
-        <v>-4.488942953468007</v>
+        <v>-1.507805511742308</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.6511751743042606</v>
       </c>
       <c r="E70">
-        <v>-8.530320264274309</v>
+        <v>-2.730685488754851</v>
       </c>
       <c r="F70">
-        <v>-2.540796809605847</v>
+        <v>0.1503849845263257</v>
       </c>
       <c r="G70">
-        <v>-3.887140669693371</v>
+        <v>-1.965936228315099</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.8140406322712479</v>
       </c>
       <c r="E71">
-        <v>-8.711921128929905</v>
+        <v>-2.677285723256402</v>
       </c>
       <c r="F71">
-        <v>-2.470939758160362</v>
+        <v>-0.001228616105859419</v>
       </c>
       <c r="G71">
-        <v>-4.718982834557558</v>
+        <v>-1.393254785880534</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.018707276090862</v>
       </c>
       <c r="E72">
-        <v>-8.868035741870333</v>
+        <v>-3.162588697236411</v>
       </c>
       <c r="F72">
-        <v>-2.808178068248874</v>
+        <v>-0.6903499435969765</v>
       </c>
       <c r="G72">
-        <v>-4.162753437022049</v>
+        <v>-2.048084891277357</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.264191122075722</v>
       </c>
       <c r="E73">
-        <v>-8.847893089484215</v>
+        <v>-3.353137826531164</v>
       </c>
       <c r="F73">
-        <v>-2.666708654831371</v>
+        <v>-0.1916545430288126</v>
       </c>
       <c r="G73">
-        <v>-4.82119616735582</v>
+        <v>-1.430854303730211</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.545858720377085</v>
       </c>
       <c r="E74">
-        <v>-8.867139104016815</v>
+        <v>-2.813583733939264</v>
       </c>
       <c r="F74">
-        <v>-2.91048061412721</v>
+        <v>-0.4182850956585209</v>
       </c>
       <c r="G74">
-        <v>-4.740120463843501</v>
+        <v>-1.813923795909144</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.8590075807038</v>
       </c>
       <c r="E75">
-        <v>-8.762830233724134</v>
+        <v>-3.307730817656254</v>
       </c>
       <c r="F75">
-        <v>-3.019383591471053</v>
+        <v>-0.005356370874009355</v>
       </c>
       <c r="G75">
-        <v>-4.153592266428079</v>
+        <v>-0.8195824145350171</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.198076709401962</v>
       </c>
       <c r="E76">
-        <v>-8.933562760761323</v>
+        <v>-4.656020554803995</v>
       </c>
       <c r="F76">
-        <v>-2.640401362853265</v>
+        <v>-0.753834364612725</v>
       </c>
       <c r="G76">
-        <v>-4.548575874089356</v>
+        <v>-0.8628190710238202</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.557659466238158</v>
       </c>
       <c r="E77">
-        <v>-10.0926528538686</v>
+        <v>-4.633219688175375</v>
       </c>
       <c r="F77">
-        <v>-3.021431315690773</v>
+        <v>-0.3208028196970751</v>
       </c>
       <c r="G77">
-        <v>-4.630366883901634</v>
+        <v>-1.163211623569424</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.930201098628693</v>
       </c>
       <c r="E78">
-        <v>-9.567540064887158</v>
+        <v>-3.705892366306662</v>
       </c>
       <c r="F78">
-        <v>-2.906867275516198</v>
+        <v>-0.5637646356729756</v>
       </c>
       <c r="G78">
-        <v>-3.887606603154812</v>
+        <v>-0.858494421008472</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.306638734245174</v>
       </c>
       <c r="E79">
-        <v>-10.59666295397429</v>
+        <v>-5.754564950428716</v>
       </c>
       <c r="F79">
-        <v>-3.200206255093351</v>
+        <v>-0.5965514174757801</v>
       </c>
       <c r="G79">
-        <v>-4.367068541085553</v>
+        <v>-0.6089443965264636</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.673703998063161</v>
       </c>
       <c r="E80">
-        <v>-10.85736720259587</v>
+        <v>-6.724084064626894</v>
       </c>
       <c r="F80">
-        <v>-3.193895752218824</v>
+        <v>-0.5750130366355902</v>
       </c>
       <c r="G80">
-        <v>-3.719378373802082</v>
+        <v>-0.8096993751979696</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.017204408659745</v>
       </c>
       <c r="E81">
-        <v>-11.89829582342101</v>
+        <v>-6.373706973705423</v>
       </c>
       <c r="F81">
-        <v>-3.094687986957347</v>
+        <v>-0.6576410283300352</v>
       </c>
       <c r="G81">
-        <v>-4.05402031698517</v>
+        <v>-0.2430127245525106</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.323206563273205</v>
       </c>
       <c r="E82">
-        <v>-11.66478053274148</v>
+        <v>-7.151599181795022</v>
       </c>
       <c r="F82">
-        <v>-3.157953718978757</v>
+        <v>-1.038231118076657</v>
       </c>
       <c r="G82">
-        <v>-4.23584592848024</v>
+        <v>0.7185065975624906</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.582389704069871</v>
       </c>
       <c r="E83">
-        <v>-12.96968296042173</v>
+        <v>-8.866156425157149</v>
       </c>
       <c r="F83">
-        <v>-3.784937550851077</v>
+        <v>-1.160993510436738</v>
       </c>
       <c r="G83">
-        <v>-3.942055193712238</v>
+        <v>-0.9080999285441572</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.787406860402378</v>
       </c>
       <c r="E84">
-        <v>-13.13549303621258</v>
+        <v>-9.194357578863059</v>
       </c>
       <c r="F84">
-        <v>-3.628845796039358</v>
+        <v>-0.3609637281196007</v>
       </c>
       <c r="G84">
-        <v>-3.971917591124744</v>
+        <v>0.1098203109561392</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.934741027655649</v>
       </c>
       <c r="E85">
-        <v>-14.95547315447327</v>
+        <v>-10.45422433253703</v>
       </c>
       <c r="F85">
-        <v>-3.510265002328609</v>
+        <v>-0.8108152731490946</v>
       </c>
       <c r="G85">
-        <v>-3.967002321228696</v>
+        <v>0.3540055381884555</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.023968394642691</v>
       </c>
       <c r="E86">
-        <v>-15.59457669117579</v>
+        <v>-10.96585585439763</v>
       </c>
       <c r="F86">
-        <v>-3.719736752576728</v>
+        <v>-0.9479448697433304</v>
       </c>
       <c r="G86">
-        <v>-3.319082468436064</v>
+        <v>1.042110511419607</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.062508329334457</v>
       </c>
       <c r="E87">
-        <v>-16.18964534662772</v>
+        <v>-12.50852580985062</v>
       </c>
       <c r="F87">
-        <v>-3.874165974011029</v>
+        <v>-1.113811359908084</v>
       </c>
       <c r="G87">
-        <v>-3.768534353984123</v>
+        <v>0.1249992418901304</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.060164476041289</v>
       </c>
       <c r="E88">
-        <v>-18.17253278884035</v>
+        <v>-14.09627672404996</v>
       </c>
       <c r="F88">
-        <v>-3.717447973442793</v>
+        <v>-1.309837878841364</v>
       </c>
       <c r="G88">
-        <v>-3.837239852217336</v>
+        <v>0.8894976154682737</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.030408956163646</v>
       </c>
       <c r="E89">
-        <v>-19.24754723352121</v>
+        <v>-15.33054854263258</v>
       </c>
       <c r="F89">
-        <v>-3.869455876958711</v>
+        <v>-1.289293538884534</v>
       </c>
       <c r="G89">
-        <v>-3.657524066184989</v>
+        <v>0.9135424070558845</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.98736729764367</v>
       </c>
       <c r="E90">
-        <v>-20.2328344942141</v>
+        <v>-17.42915660963721</v>
       </c>
       <c r="F90">
-        <v>-3.789356890945013</v>
+        <v>-1.918973706652967</v>
       </c>
       <c r="G90">
-        <v>-3.648323520932307</v>
+        <v>0.5239859398539295</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.951928896239108</v>
       </c>
       <c r="E91">
-        <v>-22.24199161414522</v>
+        <v>-18.30430232551554</v>
       </c>
       <c r="F91">
-        <v>-4.158622369927962</v>
+        <v>-2.276710796491156</v>
       </c>
       <c r="G91">
-        <v>-4.105817680522565</v>
+        <v>1.108837433052475</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.942292864264498</v>
       </c>
       <c r="E92">
-        <v>-23.82204412253153</v>
+        <v>-20.62050356858873</v>
       </c>
       <c r="F92">
-        <v>-4.383958184307095</v>
+        <v>-1.844753644096937</v>
       </c>
       <c r="G92">
-        <v>-3.440307198949749</v>
+        <v>1.19501543608973</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.975911303722145</v>
       </c>
       <c r="E93">
-        <v>-26.23722422199037</v>
+        <v>-23.72533403162372</v>
       </c>
       <c r="F93">
-        <v>-4.45432136823569</v>
+        <v>-1.633613561899579</v>
       </c>
       <c r="G93">
-        <v>-3.97968752377751</v>
+        <v>0.03658672697089257</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.067344183674515</v>
       </c>
       <c r="E94">
-        <v>-28.25243591166975</v>
+        <v>-24.7216617119473</v>
       </c>
       <c r="F94">
-        <v>-4.316573809558967</v>
+        <v>-2.148627800302894</v>
       </c>
       <c r="G94">
-        <v>-3.899041660289477</v>
+        <v>0.8581685120186955</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.235402875432833</v>
       </c>
       <c r="E95">
-        <v>-30.18552598945703</v>
+        <v>-28.8084917635456</v>
       </c>
       <c r="F95">
-        <v>-4.470273239311401</v>
+        <v>-2.281565029471561</v>
       </c>
       <c r="G95">
-        <v>-4.002777479891322</v>
+        <v>-0.2760349383267622</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.497411643362852</v>
       </c>
       <c r="E96">
-        <v>-33.07660795085597</v>
+        <v>-30.15099411091154</v>
       </c>
       <c r="F96">
-        <v>-4.376721566676238</v>
+        <v>-2.393083991073444</v>
       </c>
       <c r="G96">
-        <v>-4.212221133252237</v>
+        <v>-0.1013591086097227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.850898248099271</v>
       </c>
       <c r="E97">
-        <v>-35.49441230100226</v>
+        <v>-33.11879068623741</v>
       </c>
       <c r="F97">
-        <v>-4.671636929420918</v>
+        <v>-2.263717853778246</v>
       </c>
       <c r="G97">
-        <v>-4.290593110199574</v>
+        <v>-0.5879937968694091</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.304442173799134</v>
       </c>
       <c r="E98">
-        <v>-37.99180911030736</v>
+        <v>-36.13130367815202</v>
       </c>
       <c r="F98">
-        <v>-4.725344129981425</v>
+        <v>-2.412712156682779</v>
       </c>
       <c r="G98">
-        <v>-4.787012401149525</v>
+        <v>0.3022902051900473</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.830360451739321</v>
       </c>
       <c r="E99">
-        <v>-40.3193111602667</v>
+        <v>-38.66399541387291</v>
       </c>
       <c r="F99">
-        <v>-4.515971783821641</v>
+        <v>-2.881165520109538</v>
       </c>
       <c r="G99">
-        <v>-4.496932727965255</v>
+        <v>-0.6561808620962297</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.446567996463457</v>
       </c>
       <c r="E100">
-        <v>-41.84134485966673</v>
+        <v>-40.63016146581222</v>
       </c>
       <c r="F100">
-        <v>-4.62459560135074</v>
+        <v>-2.639258215837402</v>
       </c>
       <c r="G100">
-        <v>-5.770850592311869</v>
+        <v>-0.2739644875227525</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.076673144744742</v>
       </c>
       <c r="E101">
-        <v>-45.54628869819818</v>
+        <v>-43.35901990283438</v>
       </c>
       <c r="F101">
-        <v>-4.653983591699858</v>
+        <v>-2.675535737875603</v>
       </c>
       <c r="G101">
-        <v>-5.243502506942593</v>
+        <v>-1.523342095826279</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.788620594811524</v>
       </c>
       <c r="E102">
-        <v>-48.67634162933739</v>
+        <v>-47.3302674480979</v>
       </c>
       <c r="F102">
-        <v>-4.549631664866996</v>
+        <v>-2.250135113474542</v>
       </c>
       <c r="G102">
-        <v>-5.319298724965766</v>
+        <v>-1.187692817624441</v>
       </c>
     </row>
   </sheetData>
